--- a/pacjenci/EWA PAŃSZCZYK.xlsx
+++ b/pacjenci/EWA PAŃSZCZYK.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/EWA PAŃSZCZYK.xlsx
+++ b/pacjenci/EWA PAŃSZCZYK.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>28.09.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak z obwodowych limfocytów B z cechami klasycznego chłoniaka Hodgkina.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 58 min od podania 18F-FDG. Glikemia: 86 mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w śródpiersiu po stronie prawej przy segmencie 5 płuca prawego w przyleganiu do klipsów chirurgicznych wielkości 28x15x21mm wg PET, SUV max 6,0 [Im 107] oraz pośrodkowo za mostkiem wielkości 11x12x16mm, SUV max 4,6 [Im fuz 114]. Aktywne metabolicznie węzły chłonne: - przytchawiczy dolny prawy wielkości 16x11mm, SUV max 4,3 - podostrogowe wielkości do 17x11mm, SUV max 5,0 - wnękowe prawe wielkości do 17x13mm wg PET, SUV max do 5,0. Mierne pobudzone metabolizm FDG w węźle chłonnym pachowym lewym wielkości 14x9 mm wg PET, SUVmax 2,1. Aktywna metabolicznie przepuklina wślizgowa rozworu przełykowego zawierająca części żołądka SUVmax 5,5 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W płucu prawym nadprzeponowo w płacie dolnym i środkowym  widoczne pasmowate zmiany bliznowato-włókniste  Brzuch i miednica: Odcinkowo zwiększona aktywność metaboliczna w topografii pętli jelitowych-czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona o wielkości ok. 9x8mm. Zmiana ogniskowa - hypodensyjna w segm. 8 wątroby podprzeponowo wielkości 11x7mm - torbiel?  tłuszczak ? AML ?   Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Niejednorodny metabolizm FDG w strukturach kostnych. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym.  Inne:  Zwiększona aktywność metabolicznie w powłokach w ścianie klatki piersiowej  na poziomie żebra 6 i 7 po stronie prawej w topografii tworzącej się blizny po przebytym zabiegu, SUVmax 6,2 - procesy gojenia ? do dalszej kontroli.   Wartości referencyjne: MBPS SUVmax 2,4 Prawy płat wątroby SUVmax do 3,6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono uwidoczniono aktywny metabolicznie proces chłoniakowy po jednej stronie przepony. Pobudzenie metaboliczne w  śródpiersiu oraz w powłokach - związane z procesami gojenia ? do dalszej kontroli.   Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>6.2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>28.12.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak z obwodowych limfocytów B z cechami klasycznego chłoniaka Hodgkina. Ocena remisji choroby po 3 cyklach CHOP.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 60 min od podania 18F-FDG. Glikemia: 99mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Rozlanie wzmożony metabolizm FDG w topografii lewobocznej części podniebienia, SUV max do 10,5 [Im 50] - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca miernie powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bliznowate zmiany włókniste w segm. 4, 5, 6 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ok. 3mm zwapnienie w segm. 10 płuca prawego, przykręgosłupowo. Wydatna przepuklina wślizgowa rozworu przełykowego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiana ogniskowa - hypodensyjna w segm. 8 wątroby podprzeponowo wielkości 11x7mm - torbiel?  tłuszczak ? AML?  śledziona dodatkowa wielkości ok. 9x8mm. Nieregularne zwapnienie w górnej części trzonu macicy - uwapniony mięśniak?  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Zwiększony metabolizm FDG w strukturach kostnych- w pierwszej kolejności w związku ze stosowanym leczeniem- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ułożenie kości krzyżowej.   Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>31.03.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak z obwodowych limfocytów B z cechami klasycznego chłoniaka Hodgkina. Ocena remisji choroby po zakończeniu ChTh.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 61 min od podania 18F-FDG. Glikemia: 82 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca miernie powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bliznowate zmiany włókniste w segm. 4, 5, 6, 9 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ok. 3mm zwapnienie w segm. 10 płuca prawego, przykręgosłupowo. Wydatna przepuklina wślizgowa rozworu przełykowego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Hypodensyjna w przeglądowym badaniu TK zmiana ogniskowa w segm. 8 wątroby, podprzeponowo wielkości 11x7mm -  tłuszczak ? AML? najmniej prawdopodobna torbielka. Śledziona dodatkowa wielkości ok. 9x8mm. Nieregularne zwapnienie w górnej części trzonu macicy - uwapniony mięśniak?  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Zwiększony metabolizm FDG w strukturach kostnych- w pierwszej kolejności w związku ze stosowanym leczeniem- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ułożenie kości krzyżowej.  Inne: Zwiększony metabolizm FDG w mięśniach szyi- zmiany przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/EWA PAŃSZCZYK.xlsx
+++ b/pacjenci/EWA PAŃSZCZYK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono po 58 min od podania 18F-FDG. Glikemia: 86 mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w śródpiersiu po stronie prawej przy segmencie 5 płuca prawego w przyleganiu do klipsów chirurgicznych wielkości 28x15x21mm wg PET, SUV max 6,0 [Im 107] oraz pośrodkowo za mostkiem wielkości 11x12x16mm, SUV max 4,6 [Im fuz 114]. Aktywne metabolicznie węzły chłonne: - przytchawiczy dolny prawy wielkości 16x11mm, SUV max 4,3 - podostrogowe wielkości do 17x11mm, SUV max 5,0 - wnękowe prawe wielkości do 17x13mm wg PET, SUV max do 5,0. Mierne pobudzone metabolizm FDG w węźle chłonnym pachowym lewym wielkości 14x9 mm wg PET, SUVmax 2,1. Aktywna metabolicznie przepuklina wślizgowa rozworu przełykowego zawierająca części żołądka SUVmax 5,5 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W płucu prawym nadprzeponowo w płacie dolnym i środkowym  widoczne pasmowate zmiany bliznowato-włókniste  Brzuch i miednica: Odcinkowo zwiększona aktywność metaboliczna w topografii pętli jelitowych-czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona o wielkości ok. 9x8mm. Zmiana ogniskowa - hypodensyjna w segm. 8 wątroby podprzeponowo wielkości 11x7mm - torbiel?  tłuszczak ? AML ?   Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Niejednorodny metabolizm FDG w strukturach kostnych. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym.  Inne:  Zwiększona aktywność metabolicznie w powłokach w ścianie klatki piersiowej  na poziomie żebra 6 i 7 po stronie prawej w topografii tworzącej się blizny po przebytym zabiegu, SUVmax 6,2 - procesy gojenia ? do dalszej kontroli.   Wartości referencyjne: MBPS SUVmax 2,4 Prawy płat wątroby SUVmax do 3,6</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w śródpiersiu po stronie prawej przy segmencie 5 płuca prawego w przyleganiu do klipsów chirurgicznych wielkości 28x15x21mm wg PET, SUV max 6,0 [Im 107] oraz pośrodkowo za mostkiem wielkości 11x12x16mm, SUV max 4,6 [Im fuz 114]. Aktywne metabolicznie węzły chłonne: - przytchawiczy dolny prawy wielkości 16x11mm, SUV max 4,3 - podostrogowe wielkości do 17x11mm, SUV max 5,0 - wnękowe prawe wielkości do 17x13mm wg PET, SUV max do 5,0. Mierne pobudzone metabolizm FDG w węźle chłonnym pachowym lewym wielkości 14x9 mm wg PET, SUVmax 2,1. Aktywna metabolicznie przepuklina wślizgowa rozworu przełykowego zawierająca części żołądka SUVmax 5,5 - czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W płucu prawym nadprzeponowo w płacie dolnym i środkowym  widoczne pasmowate zmiany bliznowato-włókniste</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Odcinkowo zwiększona aktywność metaboliczna w topografii pętli jelitowych-czynnościowo? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Dodatkowa śledziona o wielkości ok. 9x8mm. Zmiana ogniskowa - hypodensyjna w segm. 8 wątroby podprzeponowo wielkości 11x7mm - torbiel?  tłuszczak ? AML ?</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Niejednorodny metabolizm FDG w strukturach kostnych. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym.  Inne:  Zwiększona aktywność metabolicznie w powłokach w ścianie klatki piersiowej  na poziomie żebra 6 i 7 po stronie prawej w topografii tworzącej się blizny po przebytym zabiegu, SUVmax 6,2 - procesy gojenia ? do dalszej kontroli.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono uwidoczniono aktywny metabolicznie proces chłoniakowy po jednej stronie przepony. Pobudzenie metaboliczne w  śródpiersiu oraz w powłokach - związane z procesami gojenia ? do dalszej kontroli.   Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>6.2</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 60 min od podania 18F-FDG. Glikemia: 99mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Rozlanie wzmożony metabolizm FDG w topografii lewobocznej części podniebienia, SUV max do 10,5 [Im 50] - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca miernie powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bliznowate zmiany włókniste w segm. 4, 5, 6 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ok. 3mm zwapnienie w segm. 10 płuca prawego, przykręgosłupowo. Wydatna przepuklina wślizgowa rozworu przełykowego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiana ogniskowa - hypodensyjna w segm. 8 wątroby podprzeponowo wielkości 11x7mm - torbiel?  tłuszczak ? AML?  śledziona dodatkowa wielkości ok. 9x8mm. Nieregularne zwapnienie w górnej części trzonu macicy - uwapniony mięśniak?  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Zwiększony metabolizm FDG w strukturach kostnych- w pierwszej kolejności w związku ze stosowanym leczeniem- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ułożenie kości krzyżowej.   Wartości referencyjne: MBPS SUVmax 2,3; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w topografii lewobocznej części podniebienia, SUV max do 10,5 [Im 50] - do kontroli miejscowej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca miernie powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bliznowate zmiany włókniste w segm. 4, 5, 6 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ok. 3mm zwapnienie w segm. 10 płuca prawego, przykręgosłupowo. Wydatna przepuklina wślizgowa rozworu przełykowego.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Zmiana ogniskowa - hypodensyjna w segm. 8 wątroby podprzeponowo wielkości 11x7mm - torbiel?  tłuszczak ? AML?  śledziona dodatkowa wielkości ok. 9x8mm. Nieregularne zwapnienie w górnej części trzonu macicy - uwapniony mięśniak?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Zwiększony metabolizm FDG w strukturach kostnych- w pierwszej kolejności w związku ze stosowanym leczeniem- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ułożenie kości krzyżowej.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>10.5</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono po 61 min od podania 18F-FDG. Glikemia: 82 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca miernie powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK, z drobnymi zwapnieniami - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bliznowate zmiany włókniste w segm. 4, 5, 6, 9 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ok. 3mm zwapnienie w segm. 10 płuca prawego, przykręgosłupowo. Wydatna przepuklina wślizgowa rozworu przełykowego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Hypodensyjna w przeglądowym badaniu TK zmiana ogniskowa w segm. 8 wątroby, podprzeponowo wielkości 11x7mm -  tłuszczak ? AML? najmniej prawdopodobna torbielka. Śledziona dodatkowa wielkości ok. 9x8mm. Nieregularne zwapnienie w górnej części trzonu macicy - uwapniony mięśniak?  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Zwiększony metabolizm FDG w strukturach kostnych- w pierwszej kolejności w związku ze stosowanym leczeniem- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ułożenie kości krzyżowej.  Inne: Zwiększony metabolizm FDG w mięśniach szyi- zmiany przeciążeniowe.  Wartości referencyjne: MBPS SUVmax 1,7; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Tarczyca miernie powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK, z drobnymi zwapnieniami - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Bliznowate zmiany włókniste w segm. 4, 5, 6, 9 i 10 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Ok. 3mm zwapnienie w segm. 10 płuca prawego, przykręgosłupowo. Wydatna przepuklina wślizgowa rozworu przełykowego.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Hypodensyjna w przeglądowym badaniu TK zmiana ogniskowa w segm. 8 wątroby, podprzeponowo wielkości 11x7mm -  tłuszczak ? AML? najmniej prawdopodobna torbielka. Śledziona dodatkowa wielkości ok. 9x8mm. Nieregularne zwapnienie w górnej części trzonu macicy - uwapniony mięśniak?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa odcinkowo z pobudzeniem metabolicznym.  Zwiększony metabolizm FDG w strukturach kostnych- w pierwszej kolejności w związku ze stosowanym leczeniem- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - najbardziej nasilone w odcinku piersiowym. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Poziome ułożenie kości krzyżowej.  Inne: Zwiększony metabolizm FDG w mięśniach szyi- zmiany przeciążeniowe.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>3.3</v>
       </c>
     </row>
